--- a/data/schede.xlsx
+++ b/data/schede.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="139">
   <si>
     <t>Timestamp</t>
   </si>
@@ -336,6 +336,244 @@
 E' richiesta una buona attitudine al lavoro di gruppo, serietà e cura dei dettagli.
 Dopo un periodo di formazione in sede, prevediamo una modalità di lavoro ibrida.</t>
   </si>
+  <si>
+    <t>MSC Technology Srl</t>
+  </si>
+  <si>
+    <t>Via Nizza 262 int 27,  10126 Turin  (Italy)</t>
+  </si>
+  <si>
+    <t>+39 3293727405</t>
+  </si>
+  <si>
+    <t>MSC TECHNOLOGY ITALIA è l’entità italiana che fornisce servizi IT a MSC Mediterranean Shipping Company S.A., leader globale nel settore dello shipping e della logistica.
+Insieme a oltre 3.000 professionisti IT in tutto il mondo, supportiamo la trasformazione digitale del Gruppo.
+La nostra entità lavora in stretta collaborazione con i team IT internazionali di MSC per supportare attività di sviluppo software, business intelligence, infrastrutture IT, operazioni di rete e sicurezza informatica, in linea con le esigenze in continua evoluzione del business.</t>
+  </si>
+  <si>
+    <t>MSC Technology offre ai giovani percorsi di academy e concrete opportunità di carriera nel settore IT.</t>
+  </si>
+  <si>
+    <t>AlmavivA group</t>
+  </si>
+  <si>
+    <t>c.schimizzi@reactive-almaviva.it</t>
+  </si>
+  <si>
+    <t>Gruppo leader italiano nell’Information &amp; Communication Technology, da oltre 40 anni Almaviva è protagonista della trasformazione digitale, accompagnando il percorso di innovazione di imprese e pubbliche amministrazioni.
+Il Gruppo opera attraverso una rete globale di società e sedi in Italia e all’estero, guidando l’evoluzione di processi e sistemi end-to-end nei settori strategici del mercato. Protagonisti digitali.</t>
+  </si>
+  <si>
+    <t>Tipologia contrattuale: Tirocinio curriculare e/o extracurriculare, contratto di Apprendistato, percorsi di Academy+training on the job.
+Sedi: Milano, Torino, Roma, Napoli, Bari, Padova. 
+Modalità di Lavoro: Ibrida</t>
+  </si>
+  <si>
+    <t>Accenture</t>
+  </si>
+  <si>
+    <t>Via Privata Nino Bonnet, 10 - 20154 - Milano (MI)</t>
+  </si>
+  <si>
+    <t>Renato Stefano</t>
+  </si>
+  <si>
+    <t>Accenture è una delle principali società di soluzioni e servizi che aiuta le organizzazioni a reinventarsi, costruendo il proprio core digitale e liberando tutto il potenziale dell’intelligenza artificiale, per generare valore in modo rapido e su larga scala. Grazie al talento delle sue 784.000 persone, agli asset e le piattaforme proprietarie e ad una rete di partnership e relazioni con l’ecosistema, Accenture supporta le organizzazioni nel creare vantaggio competitivo sostenibile.</t>
+  </si>
+  <si>
+    <t>Offriamo sia lavoro che stage che tirocinio. Sede: Torino / Milano / Roma / Napoli. Periodo di inserimento dipende dal profilo.</t>
+  </si>
+  <si>
+    <t>POST srl</t>
+  </si>
+  <si>
+    <t>Via Vincenzo Vela 18 - 10128 Torino</t>
+  </si>
+  <si>
+    <t>marketing@redabissi.com</t>
+  </si>
+  <si>
+    <t>Cosa succede quando un’icona della comunicazione incontra le nuove frontiere del tech?
+Post Srl fa parte dell'Armando Testa Factory e la nostra missione è superare i limiti della comunicazione tradizionale attraverso i new media, trasformando i processi creativi in un vero laboratorio di innovazione tecnologica.
+Non ci limitiamo a sviluppare software: progettiamo esperienze digitali interattive in cui la tecnologia diventa lo strumento per dare vita a visioni creative senza precedenti. Far parte della Factory significa operare all’interno di un ecosistema d’eccellenza, dove la solidità dei grandi progetti si combina con l’agilità di un team tecnico eterogeneo e d’avanguardia.
+Sviluppiamo ecosistemi digitali interattivi, piattaforme web evolute, installazioni immersive e applicazioni mobile per grandi brand. Lavoriamo a stretto contatto con il team creativo fin dalle prime fasi di ideazione: questo ci permette di mantenere una coerenza reale tra l’idea iniziale e la sua realizzazione tecnica.
+Il nostro stack tecnologico spazia dallo sviluppo front-end con React, Vue e Three.js, allo sviluppo mobile con React Native, fino a backend in Node.js e Python. Utilizziamo servizi cloud come Firebase, motori di rendering realtime come Unreal Engine 5 e pipeline di Intelligenza Artificiale che integrano Large Language Models, modelli di Machine Learning e sistemi di inferenza per AI generativa.
+Lavorare in Post Srl significa affrontare sfide tecnologiche reali, sperimentare continuamente con nuove tecnologie e contribuire alla creazione di esperienze digitali che uniscono creatività, design e ingegneria.</t>
+  </si>
+  <si>
+    <t>Siamo alla ricerca di Full Stack Developer interessati a lavorare su progetti digitali innovativi che uniscono creatività e tecnologia.
+Tipologia di inserimento: stage, tirocinio o opportunità di assunzione, in base al profilo e all’esperienza.
+Area/Ruolo: sviluppo web – Full Stack Developer.
+Sede di lavoro: Torino, con modalità ibrida (presenza in ufficio + lavoro da remoto).
+Periodo indicativo di inserimento: nel corso del 2026.</t>
+  </si>
+  <si>
+    <t>Lutech S.p.a</t>
+  </si>
+  <si>
+    <t>franca.scalzo@lutech.it</t>
+  </si>
+  <si>
+    <t>THE DIGITAL EVOLUTION COMPANY OF TODAY AND TOMORROW
+Progettiamo soluzioni end-to-end per la Digital Evolution gestendone ogni area, grazie alle nostre sei anime tecnologiche: LutechConsulting, LutechSolutions, LutechDigital, LutechCybersecurity, LutechServices e LutechCloud.
+Siamo motivati da una passione inesauribile per l’innovazione e una forte determinazione a superare limiti e ostacoli perché il fulcro di ogni nostro successo sono le nostre persone.
+In Lutech potrai operare all’interno di una vera community tecnologica, che contribuirai a far crescere e a migliorare con le tue competenze. Troverai un ambiente inclusivo e informale in cui nessuno è un numero e tutti siamo un valore. Diamo importanza alla diversità riconoscendo che la forza di un team risiede nelle esperienze, prospettive e background unici che ogni persona porta con sé.</t>
+  </si>
+  <si>
+    <t>Tirocinio curriculare / Stage extracurriculare 
+Sede: Torino 
+Ruolo: Development Engineering / Network Engineering
+Periodo indicativo di inserimento: Maggio</t>
+  </si>
+  <si>
+    <t>REPLY</t>
+  </si>
+  <si>
+    <t>https://www.reply.com/en/offices</t>
+  </si>
+  <si>
+    <t>m.gozzini@reply.it</t>
+  </si>
+  <si>
+    <t>Reply è una società specializzata in Consulenza, System Integration e Digital Services, 
+dedicata all’ideazione, progettazione e implementazione di soluzioni basate sui nuovi canali 
+di comunicazione e i media digitali. Reply affianca i principali gruppi industriali nella 
+definizione e nello sviluppo di modelli di business abilitati dai nuovi paradigmi tecnologici e 
+di comunicazione, quali ad esempio Intelligenza Artificiale, Big Data, Cloud Computing, 
+Digital Communication e Internet degli Oggetti, per ottimizzare ed integrare processi, 
+applicazioni e dispositivi.</t>
+  </si>
+  <si>
+    <t>Reply è un network di oltre 100 aziende specializzate in diversi ambiti del mondo IT con sedi in tutta Italia e all'estero — trovate tutte le sedi su reply.com/en/offices.
+Offriamo stage, tirocini e posizioni lavorative a seconda delle esigenze di ciascuno, con un periodo di ingresso da definire insieme al manager di riferimento in base alla posizione di interesse. Essendo un network così ampio, le opportunità sono molteplici e trasversali: tra i ruoli più ricercati per profili informatici troviamo ad esempio AI &amp; Data Engineer, Cybersecurity Specialist e Cloud Engineer.
+Tutte le posizioni aperte sono raccolte nella sezione Careers del nostro sito: reply.com/en/careers.</t>
+  </si>
+  <si>
+    <t>Syscons</t>
+  </si>
+  <si>
+    <t>C.so Vittorio Emanuele II, 12 - 10123, Torino</t>
+  </si>
+  <si>
+    <t>human.resources@syscons.it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syscons è una società di system integration che opera attraverso diverse practice, organizzate in tre principali aree: Digital Supply Chain, Business Technology e Governance, Risk Management and Compliance (GRC). In questi ambiti supportiamo medie e grandi imprese nella digitalizzazione dei processi e nell’integrazione di sistemi complessi, accompagnandole nei loro percorsi di trasformazione tecnologica.
+Siamo parte del Gruppo Impresoft e rappresentiamo un punto di riferimento all’interno del Polo SAP, con competenze che vanno dalla migrazione a SAP S/4HANA allo sviluppo di soluzioni di Digital Manufacturing e integrazione tra piattaforme. Il nostro obiettivo è creare soluzioni end-to-end che coinvolgano l’intera supply chain e i processi aziendali.
+In Syscons i giovani talenti hanno l’opportunità di lavorare su tecnologie attuali, crescere professionalmente e confrontarsi con team multidisciplinari, in un ambiente dinamico e attento alla formazione continua.
+</t>
+  </si>
+  <si>
+    <t>Tirocinio/apprendistato
+Junior Consultant
+Torino (ibrido)</t>
+  </si>
+  <si>
+    <t>Gruppo Iren</t>
+  </si>
+  <si>
+    <t>corso Svizzera,95 Torino (sede operativa)</t>
+  </si>
+  <si>
+    <t>marcello.casiroli@gruppoiren.it</t>
+  </si>
+  <si>
+    <t>Siamo una multiutility italiana che lavora ogni giorno per costruire un futuro più sostenibile, innovativo e vicino ai territori. Crediamo nelle persone come motore del cambiamento e valorizziamo competenze, crescita professionale e collaborazione. Operare in Iren significa contribuire concretamente alla transizione ecologica, facendo parte di una realtà solida, inclusiva e attenta allo sviluppo delle comunità e dei propri talenti.</t>
+  </si>
+  <si>
+    <t>Offriamo possibilità sia per tirocini sia per posizioni lavorative nei vari ambiti ICT quali cyber security, infrastrutture, aree applicative, advanced analytics, governance. Disponibilità ad accogliere gli studenti sin da subito</t>
+  </si>
+  <si>
+    <t>Eutelsat</t>
+  </si>
+  <si>
+    <t>Strada Pianezza 289, Torino / Via Centallo 72, Torino</t>
+  </si>
+  <si>
+    <t>elisa.agnolini@eutelsat.com</t>
+  </si>
+  <si>
+    <t>Eutelsat è un’azienda internazionale che opera nel settore delle telecomunicazioni satellitari. L’azienda gestisce satelliti nello spazio che permettono di trasmettere internet, televisione e dati in molte parti del mondo, anche nelle zone dove le reti terrestri non arrivano.
+Eutelsat lavora in diversi settori, come media e televisione, connettività internet, servizi per governi, aviazione e trasporti marittimi. Utilizza tecnologie avanzate come satelliti geostazionari (GEO) e satelliti in orbita bassa (LEO), insieme a stazioni terrestri che collegano i satelliti alle reti di comunicazione sulla Terra.
+In questo modo l’azienda contribuisce a garantire connessione e comunicazione globale tra persone, aziende e istituzioni.
+Per lavorare in aziende come Eutelsat, sono importanti soprattutto competenze informatiche e digitali che permettono di gestire le comunicazioni tra satelliti e reti terrestri.
+Le principali competenze per lavorare in azienda sono:
+- Reti e telecomunicazioni: progettazione e gestione di reti che collegano satelliti, stazioni di terra e utenti finali.
+- Programmazione e sviluppo software: creazione di programmi e sistemi che controllano i satelliti e gestiscono la trasmissione dei dati.
+- Gestione dei dati e cloud: elaborazione e archiviazione dei grandi volumi di dati trasmessi dai satelliti.
+- Cybersecurity: protezione delle comunicazioni satellitari da accessi non autorizzati o attacchi informatici.
+- Sistemi distribuiti e infrastrutture digitali: integrazione tra satelliti, server e reti terrestri per garantire connessioni stabili.
+Queste competenze permettono agli informatici di sviluppare e mantenere i sistemi digitali che rendono possibile la comunicazione satellitare globale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lavori/stage/apprendistati, su Torino, modalità ibrida (on-site in caso di stage), autunno 2026, aree: IT infrastructure, Broadband Services </t>
+  </si>
+  <si>
+    <t>WAVE INFORMATICA</t>
+  </si>
+  <si>
+    <t>VIA DON CAUSTICO, 125</t>
+  </si>
+  <si>
+    <t>MARIA NIGRO</t>
+  </si>
+  <si>
+    <t>LA WAVE INFORMATICA DAL 2000 SUPPORTA LE AZIENDE NELLA TRASFORMAZIONE DIGITALE DI PMI, ENTI PUBBLICI, REALTA' INDUSTRIALI CON PROGETTI SOFTWARE PERSONALIZZATI, SOLUZIONE DI INTELLIGENZA ARTIFICIALE E APPLICAZIONI MOBILI. PERSEGUIAMO LA QUALITA' NEI NOSTRI PRODOTTI SOFTWARE. 
+IL NOSTRO TEAM DI OLTRE 40 PROFESSIONISTI, ALTAMENTE QUALIFICATI, LAVORA IN UN'OTTICA DI COLLABORAZIONE, REALIZZANDO PROGETTI CHIAVI IN MANO E APPLICANDO METODOLOGIE AGILE PER AFFRONTARE SFIDE COMPLESSE IN AMBITO SOFTWARE E SISTEMI INTELLIGENTI. OLTRE ALLO SVILUPPO SOFTWARE, OPERIAMO ANCHE COME WEB AGENCY, OFFRENDO SITI WEB, SEO E WEB MARKETING PER AUMENTARE LA VISIBILITA' E LA CRESCITA ON LINE DEI NOSTRI CLIENTI.</t>
+  </si>
+  <si>
+    <t>LAVORO - STAGE - TIROCINIO da settembre 2026 in poi</t>
+  </si>
+  <si>
+    <t>Do IT Systems srl</t>
+  </si>
+  <si>
+    <t>Via Alessandro Antonelli 10, 10093, Collegno (TO), Italy</t>
+  </si>
+  <si>
+    <t>hr-it@doitnowgroup.com</t>
+  </si>
+  <si>
+    <t>Do IT Systems, azienda italiana del gruppo Do IT Now, è una società focalizzata sui servizi HPC (High Performace Computing): ci occupiamo di tecnologie utilizzate dai computer/cluster per creare sistemi di elaborazione ad alte prestazioni. 
+Siamo inoltre specializzati in Cloud Solution Design per l’HPC. 
+Il team di Do IT è composto da esperti HPC e ICT.
+Le principali core competence richieste riguardano: distribuzione Linux, linguaggi di programmazione Bash e Python, conoscenza di Ansible e Terraform. 
+Per le attività legate alle soluzione cloud, si richiede la conoscenza di AWS e Azure.</t>
+  </si>
+  <si>
+    <t>Offriamo contratti di: stage, tirocinio, apprendistato e lavoro a tempo determinato/indeterminato. 
+Profili: System Administrator Linux, Cloud Architect, HPC System Engineer, JR Technical Sales, ecc
+Headquarter Torino-Collegno, seconda sede a Maranello
+Modalità di lavoro: in sede e ibrido
+Periodo di inserimento: da subito</t>
+  </si>
+  <si>
+    <t>AerariumChain (progetto di Werea Srl)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Corso Valdocco, 2 - 10122 Torino</t>
+  </si>
+  <si>
+    <t>stage@aerariumchain.com</t>
+  </si>
+  <si>
+    <t>AerariumChain è una piattaforma  di Werea Srl che sviluppa soluzioni digitali avanzate per la digitalizzazione, conservazione e valorizzazione del patrimonio culturale. Combinando scansione 3D, piattaforma cloud, e tecnologie avanzate quali intelligenza artificiale e blockchain per digitalizzare opere, ofrriamo strumenti per:  Digitalizzazione 3D di opere d’arte, Creazione di gemelli digitali (Unique Virtual Image), Monitoraggio dello stato di conservazione ( AI), Certificazione e tracciabilità dei dati (blockchain), valorizzazione e fundraising per musei (NFTMicro)
+Operiamo all’intersezione tra tecnologia, ricerca e cultura, collaborando con università, enti di ricerca e istituzioni del settore culturale.</t>
+  </si>
+  <si>
+    <t>Cerchiamo studenti e studentesse per stage/tirocini curriculari, tesi e collaborazioni su progetti legati a digitalizzazione 3D, piattaforme cloud, AI applicata ai beni culturali, gestione di asset e metadati digitali, integrazione blockchain e strumenti software per musei e istituzioni culturali. Siamo interessati in particolare a profili orientati a sviluppo software, AI/data, integrazione di piattaforme digitali, UX/UI e prototipazione di servizi innovativi. 
+Sede principale: lavoro da remoto  
+Periodo indicativo di inserimento: da primavera 2026 o comunque da definire sulla base delle esigenza dello studente
+Prerequisiti Richiesti allo Studente/Competenze Tecniche Attese in Ingresso
+Conoscenza base di linguaggi di programmazione, API sviluppata in Node JS – My SQL DB 
+Conoscenza curriculare di Python e di almeno un framework di deep learning tra TensorFlow, PyTorch o Scikit-Learn.
+Capacità di lavorare in autonomia
+Forte interesse per il settore
+Requisiti preferenziali
+Familiarità con tecniche di elaborazione di dati 3D, come segmentazione, clustering e feature extraction su point cloud.
+Conoscenza di base di algoritmi di Machine Learning e Deep Learning
+Conoscenza di librerie per la manipolazione di dati 3D, come Open3D o PCL.</t>
+  </si>
 </sst>
 </file>
 
@@ -344,7 +582,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -355,6 +593,11 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Roboto"/>
     </font>
   </fonts>
   <fills count="2">
@@ -371,7 +614,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -386,6 +629,15 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,7 +718,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G16" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G28" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="Nome Azienda" id="2"/>
@@ -1050,10 +1302,283 @@
         <v>17</v>
       </c>
     </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="5">
+        <v>46091.45466131944</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="5">
+        <v>46091.87128449074</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="5">
+        <v>46092.52471219907</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" customHeight="1">
+      <c r="A20" s="5">
+        <v>46092.53051986111</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" customHeight="1">
+      <c r="A21" s="5">
+        <v>46092.53701878472</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="5">
+        <v>46092.69881454861</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="A23" s="5">
+        <v>46093.650522199074</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="A24" s="5">
+        <v>46093.65822109954</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" ht="22.5" customHeight="1">
+      <c r="A25" s="5">
+        <v>46093.659193831016</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" ht="22.5" customHeight="1">
+      <c r="A26" s="5">
+        <v>46094.40862148148</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" ht="22.5" customHeight="1">
+      <c r="A27" s="5">
+        <v>46094.62272385416</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" ht="22.5" customHeight="1">
+      <c r="A28" s="5">
+        <v>46094.78584547454</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="C22"/>
+  </hyperlinks>
+  <drawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/schede.xlsx
+++ b/data/schede.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="149">
   <si>
     <t>Timestamp</t>
   </si>
@@ -573,6 +573,60 @@
 Familiarità con tecniche di elaborazione di dati 3D, come segmentazione, clustering e feature extraction su point cloud.
 Conoscenza di base di algoritmi di Machine Learning e Deep Learning
 Conoscenza di librerie per la manipolazione di dati 3D, come Open3D o PCL.</t>
+  </si>
+  <si>
+    <t>aizoon technology &amp; consulting</t>
+  </si>
+  <si>
+    <t>Strada del Lionetto 6, Torino</t>
+  </si>
+  <si>
+    <t>annabarbara.saba@aizoongroup.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aizoOn è una società italiana di consulenza tecnologica di innovazione, indipendente, che opera a livello globale. È presente con proprie sedi in Europa, Nord America, Australia.  
+Sostiene il futuro dei suoi Clienti nell’era digitale apportando competenza di tecnologia e di innovazione e rispondendo alle loro specifiche esigenze grazie ad un’ampia capacità di intervento articolata in: Servizi di consulenza e Progetti chiavi in mano, Soluzioni, Piattaforme e Prodotti, Programmi ecosistemici.
+aizoOn si distingue per la capacità di intervento end-to-end basata sulla competenza ed eccellenza tecnologica, sulla prossimità al Cliente e sulla capacità di identificare ed applicare soluzioni innovative. È organizzata in:
+•	Innovation Stream
+Aree di interesse multi-settoriale dove diversi stakeholders condividono obiettivi comuni, perseguiti attraverso gli ecosistemi digitali: un insieme di competenze e tecnologie interconnesse dal "back-bone" digitale. I sette stream individuati da aizoOn sono: AgriFood4Life, Energy Transition, Future Manufacturing, Health4All, Human Centric Society, Resilient Ecosystem, Space4Humans.
+Gli Stream sono ancorati ai principali obiettivi indicati dall’Agenda 2030 delle Nazioni Unite.
+•	Market Division
+Assicurano un’approfondita ed assidua conoscenza delle necessità e delle trasformazioni in atto nei settori di business presidiati: Finance, Government, Aerospace, Defense e Naval, Transportation, Consumer Goods &amp; Services, Industrial Goods &amp; Communication, Energy &amp; Environment, Health &amp; Life Science.
+•	Technology Division: Artificial Intelligence &amp; Data Science
+Sviluppa soluzioni end-to-end "from data to action", integrando funzionalità di data engineering e data science con algoritmi e componenti di AI innovative e ad alta specializzazione. 
+La Divisione vanta un’esperienza consolidata nell’intero percorso di innovazione, coprendo i diversi livelli di maturità tecnologica (R&amp;S, Proof of Concept e Prototipi, Soluzioni Integrate).
+•	Technology Division: Cyber Security Division
+Sviluppa piattaforme tecnologiche proprietarie per rispondere alle attuali sfide del mondo cyber: analisi del malware, data leaks, cyber defense, monitoraggio del traffico di rete. Offre servizi ed attività di consulenza nelle aree Risk Analysis &amp; Management, Security Assessment, Governance &amp; Compliance. Accompagna le organizzazioni nella costruzione ed implementazione della propria “Security Roadmap”.
+•	Technology Division: Digital Manufacturing
+Supporta i clienti nel percorso di digitalizzazione dei processi produttivi. Copre l’intera filiera dei software industriali, dall’automazione delle macchine fino a MES e APS, combinando l’esperienza come system integrator di diversi provider di soluzioni con la capacità di sviluppare soluzioni custom internamente. L’offerta copre tutte le fasi di un progetto: assessment, analisi, integrazione, personalizzazione, test, go-live e supporto a lungo termine. Collabora inoltre con le altre divisioni tecnologiche per fornire livelli di acquisizione dati utili ai progetti di IA e sostenibilità in ambito manifatturiero.
+•	Technology Division: Next Information Technology
+Rende disponibili tutte le competenze necessarie a erogare servizi e attività di progettazione, sviluppo e manutenzione di applicazioni software e accompagna le organizzazioni nella «modernizzazione» e automazione del proprio parco applicativo grazie ad un ampio e solido presidio di competenze trasversali quali: Cloud Architecture, Database Administration, UX/UI design.
+•	Technology Division: SustAInability
+La Divisione nasce con l’obiettivo di accompagnare le aziende nella transizione verso modelli produttivi più sostenibili, circolari ed efficienti, mettendo a disposizione competenze scientifiche, metodologiche e tecnologiche che trasformano la sostenibilità in valore concreto e misurabile. Il nostro approccio integra l’Analisi del Ciclo di Vita (LCA) con i principi della circolarità e del cradle to cradle.
+aizoOn risponde alle sfide del nuovo contesto digitale facendo proprio l’approccio eco-sistemico: l’innovazione si realizza attraverso un processo di co-creazione che coinvolge sinergicamente istituzioni, cittadini, organizzazione pubbliche e private. Collabora con partner tecnologici e di ricerca scientifica innovativi e, attraverso le sue società è oggi un player globale nel processo di costruzione del valore per il Cliente.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aizoon offre opportunità di inserimento in tirocinio curriculare, extracurriculare e collaborazioni finalizzate alla tesi all'interno delle sue diverse aree, con particolare riferimento alla Divisioni Tecnologiche, in modalità cross dal punto di vista territoriale, poichè fornisce l'opportunità agli studenti di gestire le attività anche da remoto. E' disponibile inoltre ad incontrare giovani professionisti/e che hanno maturato un'iniziale esperienza per valorizzarla, valutandone la coerenza in relazione al cluster di opportunità rivolte a figure jr, presenti trasversalmente rispetto agli ambiti e ai territori presidiati.  </t>
+  </si>
+  <si>
+    <t>ORBYTA TECH</t>
+  </si>
+  <si>
+    <t>Piazza Castello 113</t>
+  </si>
+  <si>
+    <t>francesca.capobianco@orbyta.it</t>
+  </si>
+  <si>
+    <t>In ORBYTA TECH, il nostro obiettivo è trasformare la passione per l’IT in innovazione concreta.
+Siamo specializzati nella consulenza IT, sia applicativa sia sistemistica, e sviluppiamo progetti all’avanguardia in ambiti come Intelligenza Artificiale, Cloud, Realtà Virtuale, Data Science e UX/UI.
+Ci occupiamo della progettazione, implementazione e manutenzione di sistemi software, hardware e IoT, con l’obiettivo costante di soddisfare e superare le aspettative dei nostri clienti.
+La nostra sede principale si trova nel cuore di Torino, un ambiente dinamico e stimolante che riflette il nostro spirito innovativo e orientato alle persone. Da questo hub centrale, i nostri team collaborano a stretto contatto per offrire eccellenza tecnologica e guidare progetti di trasformazione digitale innovativi in diversi settori.
+Promuoviamo la crescita dei giovani talenti offrendo un ambiente stimolante, ricco di opportunità di apprendimento e della possibilità di lavorare su progetti innovativi. Crediamo nella condivisione della conoscenza e nei programmi di mentorship. Investiamo nella formazione continua attraverso la nostra academy interna, Uniqversity, che offre percorsi di sviluppo tecnico e di soft skill pensati per valorizzare il potenziale di ogni persona.</t>
+  </si>
+  <si>
+    <t>Stage, Tirocinio, Lavoro, IT Developer, MKT Specialist, UI Designer, aprile 2026</t>
   </si>
 </sst>
 </file>
@@ -718,7 +772,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G28" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G30" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="Nome Azienda" id="2"/>
@@ -1572,6 +1626,52 @@
         <v>17</v>
       </c>
     </row>
+    <row r="29" ht="22.5" customHeight="1">
+      <c r="A29" s="5">
+        <v>46096.479352766204</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" customHeight="1">
+      <c r="A30" s="5">
+        <v>46097.48528957176</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="C22"/>
